--- a/per-stock/UEC/financials.xlsx
+++ b/per-stock/UEC/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6691513344</v>
+        <v>5887551488</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6207023616</v>
+        <v>5457276928</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-818.83624</v>
+        <v>-116.22955</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>331.26303</v>
+        <v>291.46295</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -623,7 +632,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.1664901</v>
+        <v>-6.2965803</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -653,7 +662,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.07121</v>
+        <v>-0.0896</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -667,8 +676,10 @@
           <t>Revenue growth (YoY)</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>-0.594</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>(missing — see Data flags)</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -683,7 +694,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>486347008</v>
+        <v>488052992</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -698,7 +709,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1857000</v>
+        <v>1913000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -713,11 +724,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-87524128</v>
+        <v>-120234000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -743,7 +754,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13.65</v>
+        <v>12.01</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +798,465 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D54</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C54</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B54</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B54:E54)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D52</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C52</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B52</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B52:E52)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B41:E41)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B4:E4)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1918,13 +2388,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1934,6 +2404,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1944,30 +2415,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -1980,21 +2456,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-219148.772195</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2357200</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>1079272.958489</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>70547.292629</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-948570</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-969673.469388</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2003,21 +2480,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.011258</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.060678</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.016255</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.122449</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2026,21 +2504,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-31257000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-17619000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-26594000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-29997000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-23449000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-2404000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2049,21 +2528,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-19466000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>5893000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>17787000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>4340000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-4517000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-7919000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2072,21 +2552,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-19466000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>5893000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>17787000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>4340000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-4517000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-7919000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2095,21 +2576,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-52344000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-13937000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-10341000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-27052000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-30212000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-10234000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2118,21 +2600,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>1705000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>1479000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>1430000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>1408000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>1050000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2141,10 +2624,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>10172000</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -2153,9 +2636,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>31519000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2164,21 +2648,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-50723000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-11726000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>-8807000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-25657000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-27966000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-10323000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2187,21 +2672,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-52538000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-13431000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-10286000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-27087000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-29374000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-11373000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2210,21 +2696,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>3819000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>3403000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>2040000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>713000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>167000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>912000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2233,21 +2720,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>402000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>723000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>412000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>404000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>289000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2256,21 +2744,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>4221000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>3903000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>2763000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>1125000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>571000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>1201000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2279,21 +2768,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-33097148.772195</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-17472800</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-27048727.041511</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-31321452.707371</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-26643570</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-3284673.469388</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2302,21 +2792,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-52344000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-13937000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-10341000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-27052000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-30212000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-10234000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2325,21 +2816,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>40748000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>43649000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>30071000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>32954000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>23211000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>53410000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2348,19 +2840,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>195000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>76000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>455000</v>
       </c>
-      <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n">
+        <v>139000</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>163000</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>112000</v>
-      </c>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2369,21 +2864,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-40786000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-23563000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-29822000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-33020000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-23463000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-3634000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2392,21 +2888,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>490701053</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>484086707</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>467942060</v>
       </c>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n">
         <v>429941797</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="G20" s="3" t="n">
         <v>423199789</v>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>412138998</v>
-      </c>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2415,21 +2912,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>490701053</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>484086707</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>467942060</v>
       </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n">
         <v>429941797</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="G21" s="3" t="n">
         <v>423199789</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>412138998</v>
-      </c>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2438,21 +2936,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-0.03</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="G22" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2461,21 +2960,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-0.03</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="G23" s="3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>-0.05</v>
-      </c>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2484,21 +2984,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-52344000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-13937000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-10341000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-27052000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-30212000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-10234000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2507,21 +3008,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-52344000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-13937000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-10341000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-27052000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-30212000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-10234000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2530,21 +3032,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-52344000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-13937000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-10341000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-27052000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-30212000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-10234000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2553,21 +3056,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-52344000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-13937000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-10341000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-27052000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-30212000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-10234000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2576,21 +3080,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-52344000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-13937000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-10341000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-27052000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-30212000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-10234000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2599,21 +3104,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-596000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-668000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-447000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>434000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-1428000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2622,21 +3128,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-52940000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-13931000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-11009000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-27499000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-29778000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-11662000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2645,21 +3152,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-16011000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>6115000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>17022000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>4742000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-6734000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-8914000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2668,21 +3176,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>12000</v>
       </c>
       <c r="D32" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>4000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>39000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>18000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2691,21 +3200,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>1943000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>1517000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-126000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>22000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2718,7 +3228,8 @@
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
         <v>8000</v>
       </c>
     </row>
@@ -2729,21 +3240,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>1943000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>1517000</v>
       </c>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="G35" s="3" t="n">
         <v>22000</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>5000</v>
-      </c>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2752,21 +3264,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>3450000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>210000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-777000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>398000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-2256000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-1013000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2775,21 +3288,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-19470000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>3950000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>16270000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>4466000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-4518000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-7941000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2798,21 +3312,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>3819000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>3403000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>2040000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>713000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>167000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>912000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2821,21 +3336,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>402000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>500000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>723000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>412000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>404000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>289000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2844,21 +3360,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>4221000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>3903000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>2763000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>1125000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>571000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>1201000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2867,21 +3384,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-40748000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-23449000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-30071000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-32954000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-23211000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-3660000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2890,21 +3408,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>40748000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>33477000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>30071000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>32954000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>23211000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>21886000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2913,21 +3432,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>29542000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>23680000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>20920000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>22627000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>15680000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>14243000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2936,21 +3456,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>1705000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>1479000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>1426000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>1405000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>1045000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2959,21 +3480,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>1705000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>1479000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>1426000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>1405000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>1045000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2982,21 +3504,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>9391000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>8092000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>7672000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>8901000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>6126000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>6598000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3005,21 +3528,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>9391000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>8092000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>7672000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>8901000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>6126000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>6598000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3028,21 +3552,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>4019000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>3542000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>2599000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>3285000</v>
       </c>
-      <c r="E48" s="3" t="n">
-        <v>2788000</v>
-      </c>
       <c r="F48" s="3" t="n">
-        <v>2711000</v>
+        <v>2307000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3051,19 +3576,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>440000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>317000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>342000</v>
       </c>
-      <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n"/>
       <c r="F49" s="3" t="n">
+        <v>342000</v>
+      </c>
+      <c r="G49" s="3" t="n">
         <v>305000</v>
       </c>
-      <c r="G49" s="3" t="n">
-        <v>268000</v>
-      </c>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3072,19 +3600,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>195000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>76000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>455000</v>
       </c>
-      <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n"/>
       <c r="F50" s="3" t="n">
+        <v>139000</v>
+      </c>
+      <c r="G50" s="3" t="n">
         <v>163000</v>
       </c>
-      <c r="G50" s="3" t="n">
-        <v>112000</v>
-      </c>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3093,21 +3624,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>4737000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>4157000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>4276000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>5616000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>3338000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>3419000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3116,10 +3648,10 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>10028000</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>0</v>
@@ -3128,9 +3660,10 @@
         <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>18226000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3139,10 +3672,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>10172000</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -3151,9 +3684,10 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>31524000</v>
+        <v>0</v>
       </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3162,10 +3696,10 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>20200000</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>0</v>
@@ -3174,9 +3708,10 @@
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>49750000</v>
+        <v>0</v>
       </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3185,10 +3720,10 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>20200000</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>0</v>
@@ -3197,16 +3732,17 @@
         <v>0</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>49750000</v>
+        <v>0</v>
       </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4528,7 +5064,1385 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>490220783</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>489270002</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>483209225</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>454015855</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>435027962</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>490220783</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>489270002</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>483209225</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>454015855</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>435027962</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1421481000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1412961000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1312483000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>983900000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>892792000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1421481000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1412961000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1312483000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>983900000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>892792000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>563830000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>576846000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>523420000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>207583000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>137566000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1421481000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1412961000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1312483000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>983900000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>892792000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1421481000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1412961000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1312483000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>983900000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>892792000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1421481000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1412961000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1312483000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>983900000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>892792000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1421481000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1412961000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1312483000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>983900000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>892792000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1421481000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1412961000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1312483000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>983900000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>892792000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>-11454000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-10757000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>-16949000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-14417000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-13910000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>-11454000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-10757000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-16949000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-14417000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-13910000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-483179000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-430835000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-416898000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-406557000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>-379505000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1915621000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1854064000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1745847000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1404420000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1285772000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>493000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>489000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>483000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>454000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>435000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>493000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>489000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>483000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>454000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>435000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>116575000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>119687000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>116025000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>123753000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>115018000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>98770000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>98881000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>96433000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>97320000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>99921000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1220000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1191000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1239000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1293000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>1395000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>61301000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>60760000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>62123000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>62647000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>61301000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>60760000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>62123000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>62647000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Long Term Provisions</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>36249000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>35690000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>34434000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>33904000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>35879000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>17805000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>20806000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>19592000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>26433000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>15097000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>693000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>666000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>688000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>713000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>355000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Current Provisions</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4847000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>5017000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>5160000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2845000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>12462000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>15293000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>13887000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>20560000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>11897000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n">
+        <v>9975000</v>
+      </c>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>12462000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>15293000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>13887000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>10585000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>11897000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>12462000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>15293000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>13887000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>10585000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>11897000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1538056000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1532648000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1428508000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1107653000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1007810000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>956421000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>934996000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>885496000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>873637000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>855147000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>44339000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>10107000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>10218000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>12178000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>12931000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>129661000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>143647000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>100407000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>84295000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>64329000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>65882000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>83963000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>44491000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>28470000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>8763000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>65882000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>83963000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>44491000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>28470000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>8763000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>63779000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>59684000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>55916000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>55825000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>55566000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>782421000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>781242000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>774871000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>777164000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>777887000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>-22346000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>-20921000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>-19550000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>-18298000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>-17273000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>804767000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>802163000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>794421000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>795462000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>795160000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>72491000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>69869000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>68575000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>67649000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>67177000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>2086000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2086000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>2086000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2086000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2086000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1514000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1514000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1514000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1514000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1514000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>581635000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>597652000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>543012000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>234016000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>152663000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n">
+        <v>271000</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>687000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Prepaid Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n">
+        <v>3962000</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>3840000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>86455000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>84693000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>81662000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>79279000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>76358000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Other Inventories</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>73925000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>73925000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>72899000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>72899000</v>
+      </c>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>8377000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>7227000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1668000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>73077000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>2667000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>2059000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>5599000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>3770000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>2897000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>1486000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1482000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1496000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1470000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>384000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>7127000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>26612000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>6632000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>5807000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>4908000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>7127000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>6412000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>6632000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>5807000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>4908000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>20200000</v>
+      </c>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="n"/>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>488053000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>486347000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>454718000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>148930000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>71397000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n"/>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>488053000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>486347000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>454718000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>148930000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>71397000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5648,13 +7562,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5664,6 +7578,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5674,30 +7589,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5710,21 +7630,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-21252000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-39062000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>-35437000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-24483000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>-22867000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-10018000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5733,21 +7654,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>59343000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>106093000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>342760000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>119488000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>32736000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>70642000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5756,21 +7678,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-3627000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-941000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-1128000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-1025000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-2127000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-1210000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5779,21 +7702,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>489931000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>494004000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>462375000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>158137000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>80604000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>70720000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5802,21 +7726,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>494004000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>462375000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>158137000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>80604000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>70720000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>197847000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5825,21 +7750,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-2000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-1000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>14000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-8000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5848,21 +7774,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>-4075000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>31623000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>304240000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>77534000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>9870000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>-127119000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5871,21 +7798,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>59343000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>106093000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>339677000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>119451000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>32736000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>70642000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5894,21 +7822,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>59343000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>106093000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>339677000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>119451000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>32736000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>70642000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5917,15 +7846,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
         <v>-3083000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-37000</v>
       </c>
-      <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n">
         <v>-2637000</v>
       </c>
     </row>
@@ -5936,21 +7866,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>59343000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>106093000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>342760000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>119488000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>32736000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>70642000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5959,21 +7890,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>59343000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>106093000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>342760000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>119488000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>32736000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>70642000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5982,21 +7914,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-45793000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-36349000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-1128000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-18459000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-2126000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-188953000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6005,21 +7938,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-45793000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-36349000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-1128000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-18459000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-2126000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-188953000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6029,16 +7963,17 @@
       </c>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n">
         <v>-2260000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-177292000</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="G16" s="3" t="n">
         <v>5000</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="H16" s="3" t="n">
         <v>8000</v>
       </c>
     </row>
@@ -6049,21 +7984,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-1351000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-35408000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-15174000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-10455000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6072,21 +8008,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>1168000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>66000</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6094,18 +8031,21 @@
           <t>Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
+      <c r="B19" s="3" t="n">
+        <v>-1351000</v>
+      </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n">
         <v>-15240000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>-10455000</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="H19" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6116,7 +8056,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0</v>
+        <v>-821000</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>0</v>
@@ -6125,12 +8065,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
         <v>177293000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-177293000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6139,7 +8080,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-821000</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -6148,12 +8089,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
         <v>177293000</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>-177293000</v>
-      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6162,21 +8104,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-3627000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-941000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-1128000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-1025000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-2127000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-1210000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6185,21 +8128,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-3627000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-941000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-1128000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-1025000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-2127000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-1210000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6208,21 +8152,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-17625000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-38121000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>-34309000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-23458000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-20740000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-8808000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6231,21 +8176,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-17625000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>-38121000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>-34309000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>-23458000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-20740000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-8808000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6254,21 +8200,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>15297000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-21820000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-9696000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>6101000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-228000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-8705000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6277,21 +8224,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-195000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-167000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-142000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>330000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-92000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-21000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6303,10 +8251,11 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n">
         <v>435000</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="H28" s="3" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -6317,21 +8266,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-2547000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>815000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-4473000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>7768000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>415000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-277000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6340,21 +8290,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-654000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>558000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-3004000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>93000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-161000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>891000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6363,21 +8314,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-1507000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-2826000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-2077000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-2609000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-390000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-9298000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6386,21 +8338,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>2217000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>2142000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>1678000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>1302000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>1336000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>1556000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6409,21 +8362,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>19432000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-4064000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-16021000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-4532000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>4266000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>7968000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6432,21 +8386,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>-596000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>-668000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-447000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>434000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-1429000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6455,21 +8410,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-596000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>6000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-668000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-447000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>434000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-1429000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6478,21 +8434,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>1705000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>1479000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>1430000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>1408000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>1050000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6501,21 +8458,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>1705000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>1479000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>1430000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>1408000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>1050000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6524,21 +8482,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1705000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>1479000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>1430000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>1408000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>1050000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6547,21 +8506,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-3446000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-2153000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>-740000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-260000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>2256000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>986000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6570,21 +8530,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-3454000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-2153000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-740000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-370000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>2255000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>991000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6594,9 +8555,7 @@
       </c>
       <c r="B41" s="3" t="n"/>
       <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="D41" s="3" t="n"/>
       <c r="E41" s="3" t="n">
         <v>0</v>
       </c>
@@ -6604,6 +8563,9 @@
         <v>0</v>
       </c>
       <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
         <v>-1706000</v>
       </c>
     </row>
@@ -6614,34 +8576,35 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-52344000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-13937000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-10341000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-27052000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-30212000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-10234000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6672,6 +8635,30 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue growth (YoY)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>missing from yfinance</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FY Summary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>'Net Debt' not found in statements — left blank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
